--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_handbook/lang_handbook__lore__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_handbook/lang_handbook__lore__part_0001.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Malee khoa học "Devorsonidum spiritalis", một thành viên của chi Devorsonidum. Weapons Dodgem của Pneuma Predator là một phần cấu trúc cơ thể và có thể được thu hồi bằng năng lượng khí Dodgen của chính nó sau khi Dodgem.</t>
+          <t>Malee khoa học "Devorsonidum spiritalis", một thành viên của chi Devorsonidum. Vũ khí Dodgem của Pneuma Predator là một phần cấu trúc cơ thể và có thể được thu hồi bằng năng lượng khí Dodgen của chính nó sau khi Dodgem.</t>
         </is>
       </c>
     </row>
